--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="51" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -599,14 +599,22 @@
           <t>L36: suspicious token(s): to2 (letter/digit mix) :: Letter of Defendant to2</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L51: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: r ，</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | abbreviation/spacing may be garbled :: E.F. â€¢ &gt;</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]57</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]57</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L27: isolated marker/symbol line :: 0</t>
@@ -614,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: P</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]57</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -634,7 +642,7 @@
       </c>
       <c r="W2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | abbreviation/spacing may be garbled :: E.F. â€¢ &gt;</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | abbreviation/spacing may be garbled :: E.F. • &gt;</t>
         </is>
       </c>
       <c r="X2" s="1" t="inlineStr"/>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -665,7 +673,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 1st Decemberâ€™</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | abbreviation/spacing may be garbled :: E.F. • &gt;</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,7 +685,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L56: symbol-only separator/garbage line :: 1850.</t>
+          <t>L49: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -693,7 +701,7 @@
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>L95: abbreviation/spacing may be garbled :: A.B.in theÂ§</t>
+          <t>L95: abbreviation/spacing may be garbled :: A.B.in the§</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr"/>
@@ -724,7 +732,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Letter,â€”,</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE | isolated marker/symbol line :: ■</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -736,7 +744,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 1849.</t>
+          <t>L56: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -762,12 +770,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -782,12 +790,12 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L65: symbol-only separator/garbage line :: 1849.</t>
+          <t>L51: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: r ，</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 5</t>
+          <t>L59: symbol-only separator/garbage line :: 1849.</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -829,12 +837,12 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L71: symbol-only separator/garbage line :: 1850.</t>
+          <t>L65: symbol-only separator/garbage line :: 1849.</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L103: symbol-only separator/garbage line :: 1850.</t>
+          <t>L63: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -876,12 +884,12 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L77: symbol-only separator/garbage line :: 1850.</t>
+          <t>L71: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: â–</t>
+          <t>L103: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -923,12 +931,12 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L82: symbol-only separator/garbage line :: 1850.</t>
+          <t>L77: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L124: symbol-only separator/garbage line :: 1850.</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE | isolated marker/symbol line :: ■</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -970,12 +978,12 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L88: symbol-only separator/garbage line :: 1800.</t>
+          <t>L82: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: R.</t>
+          <t>L124: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -997,7 +1005,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1017,12 +1025,12 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: a</t>
+          <t>L88: symbol-only separator/garbage line :: 1800.</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L130: symbol-only separator/garbage line :: 1800.</t>
+          <t>L126: isolated marker/symbol line :: R.</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1049,7 +1057,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1064,10 +1072,14 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: R.</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="inlineStr"/>
+          <t>L90: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>L130: symbol-only separator/garbage line :: 1800.</t>
+        </is>
+      </c>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1087,12 +1099,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1105,7 +1117,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L94: isolated marker/symbol line :: R.</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
